--- a/testdata/logindata.xlsx
+++ b/testdata/logindata.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\com.openctms.demo\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C09C45-69A5-4524-B653-9F217A63C2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{72566B1A-6548-4A43-B347-689AA4B2D5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{84D5321D-EFF5-4E7C-B067-3B0D93D7E766}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84D5321D-EFF5-4E7C-B067-3B0D93D7E766}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -509,7 +505,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
